--- a/case_studies/base_case/2030/technologies.xlsx
+++ b/case_studies/base_case/2030/technologies.xlsx
@@ -691,10 +691,10 @@
         <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>67.73999999999999</v>
+        <v>53.53</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>64.33</v>
+        <v>72.17</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0</v>
@@ -718,7 +718,7 @@
         <v>184.21</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0</v>
+        <v>36.8</v>
       </c>
       <c r="S2" s="3" t="n">
         <v>22.37</v>
@@ -733,16 +733,16 @@
         <v>49.16</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>0</v>
+        <v>23.43</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>13.37</v>
+        <v>0</v>
       </c>
       <c r="AA2" s="3" t="n">
         <v>0</v>
@@ -785,7 +785,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>0.11</v>
+        <v>0.32</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="L3" s="5" t="n">
         <v>0</v>
@@ -836,10 +836,10 @@
         <v>0</v>
       </c>
       <c r="Y3" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AA3" s="5" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>0</v>
@@ -909,7 +909,7 @@
         <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>44.5</v>
+        <v>63.68</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>0</v>
@@ -933,10 +933,10 @@
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="3" t="n">
         <v>0</v>
@@ -982,10 +982,10 @@
         <v>0</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>20.79</v>
+        <v>24.11</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>16.95</v>
+        <v>11.26</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>0</v>
@@ -1003,7 +1003,7 @@
         <v>0</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>46.87</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>84.40000000000001</v>
@@ -1012,7 +1012,7 @@
         <v>0</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>25.54</v>
+        <v>0</v>
       </c>
       <c r="T5" s="5" t="n">
         <v>0</v>
@@ -1030,7 +1030,7 @@
         <v>0</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" s="5" t="n">
         <v>0</v>
@@ -1079,10 +1079,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>67.78</v>
+        <v>55.06</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>69.23999999999999</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -1100,13 +1100,13 @@
         <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>135.57</v>
+        <v>139.37</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>135.68</v>
+        <v>139.37</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0</v>
+        <v>37.86</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>0</v>
@@ -1118,19 +1118,19 @@
         <v>0</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0</v>
+        <v>37.86</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="3" t="n">
         <v>0</v>
@@ -1203,10 +1203,10 @@
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>0</v>
+        <v>19.82</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>26.4</v>
+        <v>15.67</v>
       </c>
       <c r="T7" s="5" t="n">
         <v>0</v>
@@ -1215,16 +1215,16 @@
         <v>0</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>0</v>
+        <v>19.43</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" s="5" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>78.3</v>
+        <v>65.55</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>79.95999999999999</v>
+        <v>106.66</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>156.59</v>
+        <v>165.93</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>156.94</v>
+        <v>219.24</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0</v>
+        <v>45.07</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0</v>
+        <v>36.27</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>0</v>
@@ -1312,19 +1312,19 @@
         <v>0</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0</v>
+        <v>45.07</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="3" t="n">
         <v>0</v>
